--- a/vlearn-app/public/quiz_excel/Day_09_Multi-Agent _ A2A Systems/Day_09_Phan_03_19_Cau.xlsx
+++ b/vlearn-app/public/quiz_excel/Day_09_Multi-Agent _ A2A Systems/Day_09_Phan_03_19_Cau.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4 → o5</t>
+          <t>o2 → o4 → o5 → o1 → o3</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -702,7 +702,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Bản sửa phải quay lại verifier; không thử lại trước khi có feedback có thể hành động.</t>
+          <t>Trình tự vòng lặp phản biện và tự sửa chữa Writer–Verifier an toàn: 1. Writer tạo bản nháp ban đầu (draft) (o2) -&gt; 2. Verifier đối chiếu bản nháp với các tiêu chí/hợp đồng và trả về các vi phạm cụ thể (o4) -&gt; 3. Ghi nhận số lần thử (attempt) và phản hồi vào nhật ký trace (o5) -&gt; 4. Nếu chưa đạt và còn ngân sách thử lại, writer sửa theo feedback có tính hành động rồi gửi lại verifier (o1) -&gt; 5. Nếu đạt thì xuất bản, nếu hết ngân sách thì dừng lại và leo thang từ chối (o3).</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I7" s="4" t="n">
@@ -847,7 +847,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Thiết kế như khi gọi một danh tính ngoài tổ chức.</t>
+          <t>Khi tích hợp và gọi một agent đối tác nằm ngoài miền tin cậy (external trust boundary), bên gọi bắt buộc phải: (a) Xác thực danh tính agent/endpoint; (b) Phân quyền chặt chẽ các năng lực và dữ liệu được gửi đi; (c) Thu gọn ngữ cảnh tối thiểu (context minimization / least privilege); (d) Kiểm tra tính toàn vẹn và nguồn gốc của các artifact nhận về. Không được tin tưởng mù quáng chỉ vì agent có tên trong danh mục.</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I9" s="4" t="n">
@@ -944,7 +944,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mỗi kết quả theo contract phải có kiểm tra riêng.</t>
+          <t>Bộ kiểm thử hợp đồng độc lập (contract test suite) cho RetrievalWorker bắt buộc phải bao quát: (a) Truy vấn hợp lệ trả về kết quả đúng schema; (b) Khi không có kết quả phù hợp phải trả về tập rỗng mà không được bịa đặt; (c) Đầu vào không hợp lệ (sai schema) phải bị từ chối rõ ràng; (d) Khi các dịch vụ phụ thuộc (vector DB, embedder) gặp sự cố phải chuyển hóa thành mã lỗi có cấu trúc theo contract. Không thể chỉ chạy một test end-to-end đơn lẻ.</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4 → o5</t>
+          <t>o2 → o3 → o4 → o1 → o5</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -996,7 +996,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Định danh phải tồn tại trước snapshot và được dùng lại khi tiếp tục.</t>
+          <t>Quy trình tạm dừng, kiểm tra và tiếp tục (pause, inspect, resume) an toàn trong đồ thị tác nhân: 1. Khởi tạo bộ lưu trữ trạng thái (checkpointer) (o2) -&gt; 2. Thực thi đồ thị với thread ID duy nhất và ổn định (o3) -&gt; 3. Đồ thị dừng lại tại cổng kiểm tra (review gate / interrupt) và lưu snapshot trạng thái (o4) -&gt; 4. Tiếp tục thực thi với cùng thread/run ID từ checkpoint đã duyệt (o1) -&gt; 5. Thực hiện tác vụ có hậu quả ra bên ngoài với chốt chặn idempotent (o5).</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4,5</t>
         </is>
       </c>
       <c r="I12" s="4" t="n">
@@ -1093,7 +1093,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Người kiểm tra phải biết ai làm gì, trên đầu vào nào, kết quả/trạng thái/bao lâu.</t>
+          <t>Một bản ghi dấu vết (trace record / span) hoàn chỉnh để tái dựng trạng thái và hành động của agent/node cần: (a) Trace/Run ID; (b) Dấu thời gian (timestamp); (c) Định danh duy nhất của agent/node thực hiện; (d) Tên hành động hoặc tool được gọi; (e) Tóm tắt dữ liệu vào/ra trong phạm vi được phép; (f) Trạng thái thực thi và độ trễ (latency). Tuyệt đối không lưu trữ các bí mật bảo mật hoặc prompt thô chứa dữ liệu nhạy cảm.</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I16" s="4" t="n">
@@ -1294,7 +1294,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Một lỗi không được biến thành việc hoàn tất âm thầm.</t>
+          <t>Chính sách cô lập lỗi có kiểm soát cho worker gọi dịch vụ từ xa bao gồm: (a) Cấu hình timeout rõ ràng; (b) Thử lại có giới hạn (exponential backoff) chỉ áp dụng cho lỗi tạm thời; (c) Có phương án dự phòng bảo toàn nguồn gốc dữ liệu; (d) Cho phép trả lời một phần kèm công bố minh bạch phần dữ liệu còn thiếu. Không được thử lại vô hạn hay nuốt lỗi.</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I17" s="4" t="n">
@@ -1346,7 +1346,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Nếu đầu vào/tiêu chí đổi thì không thể quy khác biệt cho kiến trúc.</t>
+          <t>Một nghiên cứu đối chiếu hợp lệ giữa kiến trúc Single-Agent và Multi-Agent bắt buộc phải: (a) Dùng chung một bộ câu hỏi kiểm thử và tiêu chí chấm điểm đóng băng; (b) Đánh giá đa chiều trên các khía cạnh: chất lượng, độ trễ, chi phí token, và tỷ lệ từ chối/không trả lời; (c) Cung cấp khả năng chẩn đoán dấu vết chi tiết cho từng ca kiểm thử; (d) Kiểm tra kỹ lưỡng các ca hồi quy (regressions) ở cấp từng trường hợp cụ thể.</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I20" s="4" t="n">
@@ -1500,7 +1500,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chỉ chọn thứ code có thể quyết từ dữ kiện/contract đầy đủ.</t>
+          <t>Các thành phần của artifact cuối cùng có thể kiểm tra tự động bằng quy tắc xác định (deterministic rules) trước khi công bố: (a) Tính hợp lệ của cấu trúc JSON schema và các trường bắt buộc; (b) Sự tồn tại của các mã định danh tham chiếu trong cơ sở dữ liệu; (c) Tổng tỷ lệ phân bổ phần trăm đạt chính xác 100%; (d) Giá trị trạng thái thuộc danh mục enum cho phép. Diễn giải pháp lý là yếu tố chủ quan, không thể kiểm tra bằng luật xác định.</t>
         </is>
       </c>
     </row>
